--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487729_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487729_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.997299999999999</v>
+        <v>9.1975</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7053</v>
+        <v>5.9055</v>
       </c>
       <c r="F2" t="n">
         <v>3.292</v>
@@ -610,10 +610,10 @@
         <v>3.1045</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5574</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0134</v>
+        <v>0.2136</v>
       </c>
       <c r="U2" t="n">
         <v>0.544</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.981</v>
+        <v>8.827400000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3713</v>
+        <v>6.218</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6097</v>
+        <v>2.6095</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4373</v>
+        <v>9.9947</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7127</v>
+        <v>2.4782</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7247</v>
+        <v>7.5165</v>
       </c>
       <c r="J3" t="n">
-        <v>7.44</v>
+        <v>10.252</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0257</v>
+        <v>2.7188</v>
       </c>
       <c r="L3" t="n">
-        <v>6.4143</v>
+        <v>7.5332</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0027</v>
+        <v>-0.2573</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3131</v>
+        <v>-0.2406</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6896</v>
+        <v>-0.0167</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7761</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1045</v>
+        <v>-3.8806</v>
       </c>
       <c r="R3" t="n">
         <v>2.3284</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4257</v>
+        <v>0.385</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5298</v>
+        <v>-0.1534</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8959</v>
+        <v>0.5384</v>
       </c>
       <c r="V3" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8.225899999999999</v>
+        <v>8.671799999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4559</v>
+        <v>6.9564</v>
       </c>
       <c r="F4" t="n">
-        <v>1.77</v>
+        <v>1.7155</v>
       </c>
       <c r="G4" t="n">
         <v>3.7744</v>
@@ -766,13 +766,13 @@
         <v>2.5224</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3753</v>
+        <v>0.8213</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2905</v>
+        <v>0.21</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6113</v>
       </c>
       <c r="V4" t="n">
         <v>1.5537</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>8.163399999999999</v>
+        <v>7.9771</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7175</v>
+        <v>6.5309</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4459</v>
+        <v>1.4462</v>
       </c>
       <c r="G5" t="n">
-        <v>9.9947</v>
+        <v>6.4373</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4782</v>
+        <v>0.7127</v>
       </c>
       <c r="I5" t="n">
-        <v>7.5165</v>
+        <v>5.7247</v>
       </c>
       <c r="J5" t="n">
-        <v>10.252</v>
+        <v>7.44</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7188</v>
+        <v>1.0257</v>
       </c>
       <c r="L5" t="n">
-        <v>7.5332</v>
+        <v>6.4143</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2573</v>
+        <v>-1.0027</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2406</v>
+        <v>-0.3131</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0167</v>
+        <v>-0.6896</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5523</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.8806</v>
+        <v>-3.1045</v>
       </c>
       <c r="R5" t="n">
         <v>2.3284</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.279</v>
+        <v>1.4219</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6539</v>
+        <v>0.6895</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3748</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>7.6291</v>
+        <v>7.357</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9838</v>
+        <v>6.2841</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6452</v>
+        <v>1.0729</v>
       </c>
       <c r="G6" t="n">
         <v>8.311999999999999</v>
@@ -922,13 +922,13 @@
         <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>0.841</v>
+        <v>0.5689</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.2325</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3737</v>
+        <v>0.8014</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9418</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.9506</v>
+        <v>5.5205</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0983</v>
+        <v>3.5593</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8523</v>
+        <v>1.9613</v>
       </c>
       <c r="G7" t="n">
         <v>3.2424</v>
@@ -1000,13 +1000,13 @@
         <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0978</v>
+        <v>0.4722</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4116</v>
+        <v>0.0493</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3138</v>
+        <v>0.4229</v>
       </c>
       <c r="V7" t="n">
         <v>1.2239</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4.2868</v>
+        <v>4.2265</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2341</v>
+        <v>1.9955</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0527</v>
+        <v>2.231</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6745</v>
+        <v>3.1149</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6912</v>
+        <v>0.3493</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0167</v>
+        <v>2.7656</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1434</v>
+        <v>2.7889</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.1401</v>
       </c>
       <c r="L8" t="n">
-        <v>0.406</v>
+        <v>2.6489</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4688</v>
+        <v>0.326</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0462</v>
+        <v>0.2092</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4227</v>
+        <v>0.1168</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7164</v>
+        <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4376</v>
+        <v>0.0056</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4087</v>
+        <v>-0.4352</v>
       </c>
       <c r="U8" t="n">
-        <v>1.029</v>
+        <v>0.4408</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3776</v>
+        <v>0.3299</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8462</v>
+        <v>0.6119</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.4446</v>
+        <v>3.3285</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5951</v>
+        <v>1.4938</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8494</v>
+        <v>1.8347</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1149</v>
+        <v>0.6745</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3493</v>
+        <v>0.6912</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7656</v>
+        <v>-0.0167</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7889</v>
+        <v>1.1434</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1401</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>2.6489</v>
+        <v>0.406</v>
       </c>
       <c r="M9" t="n">
-        <v>0.326</v>
+        <v>-0.4688</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2092</v>
+        <v>-0.0462</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1168</v>
+        <v>-0.4227</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7463</v>
+        <v>2.7164</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7763</v>
+        <v>1.4794</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8356</v>
+        <v>0.6684</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0592</v>
+        <v>0.8109</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3299</v>
+        <v>-0.3776</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6119</v>
+        <v>0.8462</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3543</v>
+        <v>0.4694</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.1355</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2794</v>
+        <v>0.3339</v>
       </c>
       <c r="G10" t="n">
         <v>1.1547</v>
@@ -1234,13 +1234,13 @@
         <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0242</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0606</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7991</v>
+        <v>-1.6722</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9228</v>
+        <v>-2.123</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1238</v>
+        <v>0.4508</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7024</v>
@@ -1312,13 +1312,13 @@
         <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0848</v>
+        <v>0.0421</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1951</v>
+        <v>-0.0051</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2799</v>
+        <v>0.0471</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1761</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.122</v>
+        <v>-2.4891</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5543</v>
+        <v>-2.8941</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4323</v>
+        <v>0.405</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2604</v>
@@ -1390,13 +1390,13 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8668</v>
+        <v>0.4997</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3163</v>
+        <v>-0.0236</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5505</v>
+        <v>0.5232</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5642</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>51.11189999999999</v>
+        <v>51.41440000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>33.7591</v>
+        <v>34.0619</v>
       </c>
       <c r="F13" t="n">
-        <v>17.3527</v>
+        <v>17.3528</v>
       </c>
       <c r="G13" t="n">
         <v>41.29990000000001</v>
@@ -1468,16 +1468,16 @@
         <v>20.3734</v>
       </c>
       <c r="S13" t="n">
-        <v>6.2417</v>
+        <v>6.544499999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6783000000000001</v>
+        <v>0.981</v>
       </c>
       <c r="U13" t="n">
-        <v>5.5631</v>
+        <v>5.5632</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6597</v>
+        <v>0.6597000000000004</v>
       </c>
       <c r="W13" t="n">
         <v>6.917800000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>G. MORENO ABAD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.0451</v>
+        <v>-2.8508</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8335</v>
+        <v>-1.3773</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.8787</v>
+        <v>-1.4735</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.8187</v>
+        <v>-0.7409</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.898</v>
+        <v>0.4309</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.9206</v>
+        <v>-1.1717</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3384</v>
+        <v>1.2626</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4253</v>
+        <v>1.3388</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9131</v>
+        <v>-0.0762</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.1571</v>
+        <v>-2.0035</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.3233</v>
+        <v>-0.9079</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.8337</v>
+        <v>-1.0956</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7761</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.0747</v>
+        <v>-2.1344</v>
       </c>
       <c r="R14" t="n">
-        <v>3.2985</v>
+        <v>0.3881</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4318</v>
+        <v>-0.3637</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4519</v>
+        <v>-0.5056</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0202</v>
+        <v>0.1419</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. MORENO ABAD</t>
+          <t>J. BARRA DE LA CRUZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.1962</v>
+        <v>-3.7211</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4774</v>
+        <v>3.1512</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7188</v>
+        <v>-6.8723</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7409</v>
+        <v>-2.0557</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4309</v>
+        <v>-1.4179</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1717</v>
+        <v>-0.6379</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2626</v>
+        <v>5.0775</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3388</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0762</v>
+        <v>4.3895</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0035</v>
+        <v>-7.1332</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9079</v>
+        <v>-2.1058</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0956</v>
+        <v>-5.0274</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.1344</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3881</v>
+        <v>2.7164</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7091</v>
+        <v>-0.6937</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6057</v>
+        <v>-0.968</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1034</v>
+        <v>0.2743</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.5537</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1761</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BARRA DE LA CRUZ</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.9062</v>
+        <v>-3.9155</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1512</v>
+        <v>0.8326</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.0575</v>
+        <v>-4.748</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.0557</v>
+        <v>-4.8187</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4179</v>
+        <v>-0.898</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6379</v>
+        <v>-3.9206</v>
       </c>
       <c r="J16" t="n">
-        <v>5.0775</v>
+        <v>3.3384</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6879999999999999</v>
+        <v>1.4253</v>
       </c>
       <c r="L16" t="n">
-        <v>4.3895</v>
+        <v>1.9131</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.1332</v>
+        <v>-8.1571</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.1058</v>
+        <v>-2.3233</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.0274</v>
+        <v>-5.8337</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5821</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1344</v>
+        <v>-4.0747</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7164</v>
+        <v>3.2985</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8789</v>
+        <v>-0.4386</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.968</v>
+        <v>-0.5491</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0891</v>
+        <v>0.1105</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.5537</v>
+        <v>2.1179</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1761</v>
+        <v>2.1179</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.7298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.1675</v>
+        <v>-4.5797</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.5164</v>
+        <v>-2.8167</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6512</v>
+        <v>-1.763</v>
       </c>
       <c r="G17" t="n">
         <v>-3.9471</v>
@@ -1780,13 +1780,13 @@
         <v>1.5523</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3333</v>
+        <v>-0.0788</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0471</v>
+        <v>-0.3474</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3805</v>
+        <v>0.2686</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9418</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.0474</v>
+        <v>-4.6381</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2259</v>
+        <v>-0.9256</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.8215</v>
+        <v>-3.7125</v>
       </c>
       <c r="G18" t="n">
         <v>-5.3004</v>
@@ -1858,13 +1858,13 @@
         <v>1.3582</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4067</v>
+        <v>-0.9974</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7145</v>
+        <v>-0.4142</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6922</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>1.2716</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.0562</v>
+        <v>-4.7676</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7133</v>
+        <v>-2.3129</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3429</v>
+        <v>-2.4547</v>
       </c>
       <c r="G19" t="n">
         <v>-5.0621</v>
@@ -1936,13 +1936,13 @@
         <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3822</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6539</v>
+        <v>-0.2535</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2717</v>
+        <v>0.1598</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.6</v>
+        <v>-4.8147</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7743</v>
+        <v>-2.474</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8256</v>
+        <v>-2.3407</v>
       </c>
       <c r="G20" t="n">
         <v>-4.046</v>
@@ -2014,13 +2014,13 @@
         <v>1.9403</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2241</v>
+        <v>-0.4388</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.199</v>
+        <v>-0.8987000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0251</v>
+        <v>0.4599</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3299</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.8215</v>
+        <v>-7.4</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.2825</v>
+        <v>-5.1824</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5391</v>
+        <v>-2.2176</v>
       </c>
       <c r="G21" t="n">
         <v>-4.7629</v>
@@ -2092,13 +2092,13 @@
         <v>2.3284</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2243</v>
+        <v>-0.8028</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8233</v>
+        <v>-0.7232</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4011</v>
+        <v>-0.0796</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2821</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-13.2715</v>
+        <v>-13.0896</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.3477</v>
+        <v>-6.2476</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.9238</v>
+        <v>-6.842</v>
       </c>
       <c r="G22" t="n">
         <v>-10.5661</v>
@@ -2170,13 +2170,13 @@
         <v>2.5224</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1815</v>
+        <v>-0.9996</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0039</v>
+        <v>-0.9038</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1776</v>
+        <v>-0.0959</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-51.11160000000001</v>
+        <v>-49.7771</v>
       </c>
       <c r="E23" t="n">
-        <v>-17.3528</v>
+        <v>-17.3527</v>
       </c>
       <c r="F23" t="n">
-        <v>-33.7591</v>
+        <v>-32.4243</v>
       </c>
       <c r="G23" t="n">
         <v>-41.2999</v>
@@ -2224,13 +2224,13 @@
         <v>2.325800000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.8239999999999996</v>
       </c>
       <c r="L23" t="n">
         <v>1.5019</v>
       </c>
       <c r="M23" t="n">
-        <v>-43.6258</v>
+        <v>-43.62580000000001</v>
       </c>
       <c r="N23" t="n">
         <v>-13.7341</v>
@@ -2239,7 +2239,7 @@
         <v>-29.8917</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.910400000000001</v>
+        <v>-2.9104</v>
       </c>
       <c r="Q23" t="n">
         <v>-20.3735</v>
@@ -2248,16 +2248,16 @@
         <v>17.4628</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.241699999999999</v>
+        <v>-4.9071</v>
       </c>
       <c r="T23" t="n">
-        <v>-5.563499999999999</v>
+        <v>-5.5635</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6782999999999999</v>
+        <v>0.6563</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6597999999999997</v>
+        <v>-0.6597999999999999</v>
       </c>
       <c r="W23" t="n">
         <v>6.2582</v>
